--- a/tests/TeamworkDB/output/utilization_failures_report_202604.xlsx
+++ b/tests/TeamworkDB/output/utilization_failures_report_202604.xlsx
@@ -40,7 +40,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,12 +81,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,10 +453,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="51" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -461,38 +467,43 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Run: 2026-05-01   |   Passed: 32   |   Failed: 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>FORMAT ERRORS</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: EU_Utilization_Monthly</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: EU_Utilization_Monthly</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Detail</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Detail</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>MISSING TITLE</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Brussels � Manager</t>
         </is>
       </c>
     </row>
@@ -504,51 +515,51 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Brussels � Manager</t>
+          <t>Brussels � Associate-1st Yr</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>WRONG ORDER</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Brussels � expected ['Officer', 'Principal', 'Manager', 'Associate-Exp', 'Associate-1st Yr', 'Associate', 'Analyst-Exp', 'Analyst-1st Yr', 'Analyst'] but got ['Officer', 'Principal', 'Associate-Exp', 'Associate', 'Analyst-Exp', 'Analyst-1st Yr', 'Analyst']</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: EU_Utilization_YTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>MISSING TITLE</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Brussels � Associate-1st Yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>WRONG ORDER</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Brussels � expected ['Officer', 'Principal', 'Manager', 'Associate-Exp', 'Associate-1st Yr', 'Associate', 'Analyst-Exp', 'Analyst-1st Yr', 'Analyst'] but got ['Officer', 'Principal', 'Associate-Exp', 'Associate', 'Analyst-Exp', 'Analyst-1st Yr', 'Analyst']</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: EU_Utilization_YTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Detail</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Brussels � Manager</t>
         </is>
       </c>
     </row>
@@ -560,29 +571,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Brussels � Manager</t>
+          <t>Brussels � Associate-1st Yr</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>MISSING TITLE</t>
+          <t>WRONG ORDER</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Brussels � Associate-1st Yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>WRONG ORDER</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Brussels � expected ['Officer', 'Principal', 'Manager', 'Associate-Exp', 'Associate-1st Yr', 'Associate', 'Analyst-Exp', 'Analyst-1st Yr', 'Analyst'] but got ['Officer', 'Principal', 'Associate-Exp', 'Associate', 'Analyst-Exp', 'Analyst-1st Yr', 'Analyst']</t>
         </is>
@@ -599,10 +598,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -618,62 +617,92 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Run: 2026-05-01   |   Passed: 2   |   Failed: 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: 202604_US</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: 202604_US</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CRCH</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Officer</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>693.40</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>751.20</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>57.80</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>8.34%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -688,29 +717,29 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>693.40</t>
+          <t>236.80</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>751.20</t>
+          <t>250.20</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>57.80</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>8.34%</t>
+          <t>5.66%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRCH</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -720,34 +749,34 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>236.80</t>
+          <t>890,690.00</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>250.20</t>
+          <t>974,500.00</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>83,810.00</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>9.41%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -762,104 +791,104 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>890,690.00</t>
+          <t>310,827.00</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>974,500.00</t>
+          <t>329,587.00</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>83,810.00</t>
+          <t>18,760.00</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>9.41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+          <t>6.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: 2026_US (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>CRSV</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Officer</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>310,827.00</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>329,587.00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>18,760.00</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>6.04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: 2026_US (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>3,960.32</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>4,245.20</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>284.88</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>7.19%</t>
         </is>
       </c>
     </row>
@@ -876,76 +905,76 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Target_Hours</t>
+          <t>Target_Rev</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>3,960.32</t>
+          <t>3,829,251.83</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>4,245.20</t>
+          <t>4,092,784.00</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>284.88</t>
+          <t>263,532.17</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>7.19%</t>
+          <t>6.88%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRCH</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Target_Rev</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>3,829,251.83</t>
+          <t>2,658.90</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>4,092,784.00</t>
+          <t>2,918.60</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>263,532.17</t>
+          <t>259.70</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>9.77%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRSF</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -955,29 +984,29 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2,658.90</t>
+          <t>15,066.50</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2,918.60</t>
+          <t>15,622.60</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>259.70</t>
+          <t>556.10</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>9.77%</t>
+          <t>3.69%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>CRSF</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -992,22 +1021,22 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>15,066.50</t>
+          <t>15,558.50</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>15,622.60</t>
+          <t>16,029.40</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>556.10</t>
+          <t>470.90</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1048,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1029,22 +1058,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>15,558.50</t>
+          <t>3,338.30</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>16,029.40</t>
+          <t>3,515.70</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>470.90</t>
+          <t>177.40</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>5.31%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1085,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1066,22 +1095,22 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>3,338.30</t>
+          <t>3,817.40</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>3,515.70</t>
+          <t>4,045.50</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>177.40</t>
+          <t>228.10</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>5.31%</t>
+          <t>5.98%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1122,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1103,29 +1132,29 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,817.40</t>
+          <t>920.00</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>4,045.50</t>
+          <t>1,079.00</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>228.10</t>
+          <t>159.00</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>5.98%</t>
+          <t>17.28%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRCH</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1135,39 +1164,39 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>920.00</t>
+          <t>3,406,729.00</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1,079.00</t>
+          <t>3,783,294.00</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>159.00</t>
+          <t>376,565.00</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>17.28%</t>
+          <t>11.05%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRSF</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1177,29 +1206,29 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3,406,729.00</t>
+          <t>7,815,936.00</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>3,783,294.00</t>
+          <t>8,138,151.00</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>376,565.00</t>
+          <t>322,215.00</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>11.05%</t>
+          <t>4.12%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>CRSF</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -1214,22 +1243,22 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7,815,936.00</t>
+          <t>8,168,391.00</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>8,138,151.00</t>
+          <t>8,439,159.00</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>322,215.00</t>
+          <t>270,768.00</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1270,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1251,22 +1280,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8,168,391.00</t>
+          <t>2,631,599.00</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>8,439,159.00</t>
+          <t>2,784,163.00</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>270,768.00</t>
+          <t>152,564.00</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>5.80%</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1307,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1288,22 +1317,22 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2,631,599.00</t>
+          <t>3,678,480.50</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2,784,163.00</t>
+          <t>3,889,473.00</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>152,564.00</t>
+          <t>210,992.50</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>5.74%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1344,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1325,57 +1354,20 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3,678,480.50</t>
+          <t>1,186,110.00</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>3,889,473.00</t>
+          <t>1,408,710.00</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>210,992.50</t>
+          <t>222,600.00</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>5.74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>CRSV</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Officer</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>1,186,110.00</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>1,408,710.00</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>222,600.00</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>18.77%</t>
         </is>
@@ -1392,15 +1384,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1411,55 +1403,85 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Run: 2026-05-01   |   Passed: 1   |   Failed: 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRDC (Monthly)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRDC (Monthly)</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>101510</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Castro Cienfuegos, Nicolas</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>99.50</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>5.85%</t>
         </is>
       </c>
     </row>
@@ -1476,109 +1498,109 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>89,300.00</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>94,525.00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>5,225.00</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>5.85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRLA (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>101827</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Aron, Kartik</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
           <t>Actual_Hours</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>94.00</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>99.50</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>5.85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>101510</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Castro Cienfuegos, Nicolas</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>89,300.00</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>94,525.00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>5,225.00</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>5.85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRLA (Monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>214.20</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>223.20</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>4.20%</t>
         </is>
       </c>
     </row>
@@ -1595,109 +1617,109 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>93,177.00</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>97,092.00</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>3,915.00</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>4.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRNY (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>101697</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Lehrer, Nimrod David</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
           <t>Actual_Hours</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>214.20</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>223.20</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>4.20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>101827</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Aron, Kartik</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>93,177.00</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>97,092.00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>3,915.00</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>4.20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRNY (Monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>79.90</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>14.10</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>17.65%</t>
         </is>
       </c>
     </row>
@@ -1714,203 +1736,203 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>68,714.00</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>80,840.00</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>12,126.00</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>17.65%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRSF (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>101650</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Li, Lily</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
           <t>Actual_Hours</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>79.90</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>94.00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>14.10</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>17.65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>101697</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Lehrer, Nimrod David</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>68,714.00</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>80,840.00</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>12,126.00</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>17.65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRSF (Monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>33.20</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>38.20</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>15.06%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRUK (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Util Report</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Diff%</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>101650</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Li, Lily</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Actual_Hours</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>33.20</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>38.20</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>15.06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRUK (Monthly)</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>0531</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Tilson, Hannah</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>159.60</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>168.00</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>0531</t>
+          <t>101659</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Tilson, Hannah</t>
+          <t>Honnor, Kaman</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1920,17 +1942,17 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>159.60</t>
+          <t>114.00</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>168.00</t>
+          <t>120.00</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1942,12 +1964,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>101659</t>
+          <t>101963</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Honnor, Kaman</t>
+          <t>Chakma, Tridevi</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1957,17 +1979,17 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>114.00</t>
+          <t>152.00</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>120.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1976,73 +1998,53 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>101963</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Chakma, Tridevi</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>152.00</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>160.00</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>MISSING ROWS</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRB  (Monthly)</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRB  (Monthly)</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>101967</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2056,27 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>101967</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Marcus, David</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRB</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2088,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2083,17 +2100,27 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>101967</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2132,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>101967</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 4.8</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2159,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2130,46 +2167,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>5196</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet: </t>
+        </is>
+      </c>
+    </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sheet: </t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>101967</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2228,27 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>101967</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Marcus, David</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRB</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2260,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2210,17 +2272,27 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>101967</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2232,12 +2304,22 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>101967</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 4.8</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2331,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2257,46 +2339,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>5196</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRCH (Monthly)</t>
+        </is>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRCH (Monthly)</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>101899</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2400,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2325,29 +2417,54 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Ricchetti, Bryan</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRCH</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2359,12 +2476,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2503,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2384,46 +2511,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 57.800000000000004</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Chicago</t>
+        </is>
+      </c>
+    </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Chicago</t>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>101899</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2572,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -2452,29 +2589,54 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Ricchetti, Bryan</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRCH</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2486,12 +2648,22 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2675,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -2511,46 +2683,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 57.800000000000004</t>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRDC (Monthly)</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRDC (Monthly)</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>101993</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2744,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2574,17 +2756,27 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2788,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2604,46 +2796,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>5936</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="73"/>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRNY (Monthly)</t>
+        </is>
+      </c>
+    </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRNY (Monthly)</t>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>101334</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2857,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>101334</t>
+          <t>101692</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -2667,17 +2869,27 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>101692</t>
+          <t>101334</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2901,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>101334</t>
+          <t>101692</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2697,105 +2909,125 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>101692</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="80"/>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRSF (Monthly)</t>
+        </is>
+      </c>
+    </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRSF (Monthly)</t>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>101226</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>101226</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRSV (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
           <t>MISSING IN DB</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>101226</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>101226</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="85"/>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRSV (Monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>101515</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -2807,12 +3039,27 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>101515</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Feitzinger, Kristin</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRMP</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
@@ -2824,7 +3071,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -2836,17 +3083,27 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>101515</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2858,12 +3115,22 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>101515</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 13.4</t>
         </is>
       </c>
     </row>
@@ -2875,7 +3142,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -2883,46 +3150,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>6063</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="94"/>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: SV</t>
+        </is>
+      </c>
+    </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: SV</t>
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>101515</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -2934,12 +3211,27 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>101515</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Feitzinger, Kristin</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRMP</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
@@ -2951,7 +3243,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -2963,17 +3255,27 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>101515</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2985,12 +3287,22 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>101515</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 13.4</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3314,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -3010,21 +3322,14 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>6063</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -3039,15 +3344,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3058,55 +3363,85 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Run: 2026-05-01   |   Passed: 1   |   Failed: 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRDC (YTD)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRDC (YTD)</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>101400</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Boboshko, Nikolai</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>610.50</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>325.60</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>284.90</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>46.67%</t>
         </is>
       </c>
     </row>
@@ -3123,22 +3458,22 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Target_Hours</t>
+          <t>Target_Rev</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>610.50</t>
+          <t>564,712.50</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>325.60</t>
+          <t>301,180.00</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>284.90</t>
+          <t>263,532.50</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -3160,27 +3495,27 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Target_Rev</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>564,712.50</t>
+          <t>581.10</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>301,180.00</t>
+          <t>353.00</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>263,532.50</t>
+          <t>228.10</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>46.67%</t>
+          <t>39.25%</t>
         </is>
       </c>
     </row>
@@ -3197,22 +3532,22 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>581.10</t>
+          <t>537,517.50</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>353.00</t>
+          <t>326,525.00</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>228.10</t>
+          <t>210,992.50</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -3221,85 +3556,85 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>101400</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Boboshko, Nikolai</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>537,517.50</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>326,525.00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>210,992.50</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>39.25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRLA (YTD)</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRLA (YTD)</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>101597</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Ling, Anthony</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>543.00</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>319.00</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>224.00</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>41.25%</t>
         </is>
       </c>
     </row>
@@ -3316,22 +3651,22 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Target_Hours</t>
+          <t>Target_Rev</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>543.00</t>
+          <t>263,355.00</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>319.00</t>
+          <t>154,715.00</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>224.00</t>
+          <t>108,640.00</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -3353,27 +3688,27 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Target_Rev</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>263,355.00</t>
+          <t>651.60</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>154,715.00</t>
+          <t>384.90</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>108,640.00</t>
+          <t>266.70</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>41.25%</t>
+          <t>40.93%</t>
         </is>
       </c>
     </row>
@@ -3390,22 +3725,22 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>651.60</t>
+          <t>316,026.00</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>384.90</t>
+          <t>186,677.00</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>266.70</t>
+          <t>129,349.00</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -3414,85 +3749,85 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>101597</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Ling, Anthony</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>316,026.00</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>186,677.00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>129,349.00</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>40.93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRNY (YTD)</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRNY (YTD)</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>101788</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Rocafort, Roland</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>604.00</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>458.00</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>146.00</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>24.17%</t>
         </is>
       </c>
     </row>
@@ -3509,22 +3844,22 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Target_Hours</t>
+          <t>Target_Rev</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>604.00</t>
+          <t>347,300.00</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>458.00</t>
+          <t>263,350.00</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>146.00</t>
+          <t>83,950.00</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -3536,49 +3871,49 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>101788</t>
+          <t>101697</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Rocafort, Roland</t>
+          <t>Lehrer, Nimrod David</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Target_Rev</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>347,300.00</t>
+          <t>459.20</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>263,350.00</t>
+          <t>473.30</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>83,950.00</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>24.17%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>101697</t>
+          <t>101788</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Lehrer, Nimrod David</t>
+          <t>Rocafort, Roland</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -3588,71 +3923,71 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>459.20</t>
+          <t>555.20</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>473.30</t>
+          <t>402.10</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>153.10</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>27.58%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>101788</t>
+          <t>101697</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Rocafort, Roland</t>
+          <t>Lehrer, Nimrod David</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>555.20</t>
+          <t>394,912.00</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>402.10</t>
+          <t>407,038.00</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>153.10</t>
+          <t>12,126.00</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27.58%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>101697</t>
+          <t>101788</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Lehrer, Nimrod David</t>
+          <t>Rocafort, Roland</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3662,198 +3997,198 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>394,912.00</t>
+          <t>319,240.00</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>407,038.00</t>
+          <t>231,208.00</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>12,126.00</t>
+          <t>88,032.00</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>101788</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Rocafort, Roland</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>319,240.00</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>231,208.00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>88,032.00</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
           <t>27.58%</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRSF (YTD)</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRSF (YTD)</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>101650</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Li, Lily</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>165.70</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>170.70</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRUK (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Util Report</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Diff%</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>101650</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Li, Lily</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Actual_Hours</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>165.70</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>170.70</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>3.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRUK (YTD)</t>
-        </is>
-      </c>
-    </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>0531</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Tilson, Hannah</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>630.80</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>664.00</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>33.20</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>0531</t>
+          <t>101659</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Tilson, Hannah</t>
+          <t>Honnor, Kaman</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3863,17 +4198,17 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>630.80</t>
+          <t>585.20</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>664.00</t>
+          <t>616.00</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>30.80</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -3885,12 +4220,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>101659</t>
+          <t>101963</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Honnor, Kaman</t>
+          <t>Chakma, Tridevi</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3900,17 +4235,17 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>585.20</t>
+          <t>547.20</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>616.00</t>
+          <t>576.00</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>30.80</t>
+          <t>28.80</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -3919,73 +4254,53 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>101963</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Chakma, Tridevi</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>547.20</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>576.00</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>28.80</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>MISSING ROWS</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRB  (YTD)</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRB  (YTD)</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>101626</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -3997,7 +4312,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>101626</t>
+          <t>101728</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4014,7 +4329,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>101728</t>
+          <t>101763</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -4031,7 +4346,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4048,29 +4363,54 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>101885</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Marcus, David</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRB</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4422,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>101626</t>
+          <t>101728</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4449,22 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>101728</t>
+          <t>101763</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4116,12 +4476,22 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>101788</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 170.0</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 157.3</t>
         </is>
       </c>
     </row>
@@ -4133,12 +4503,22 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>101788</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4530,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>101885</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -4158,46 +4538,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>2252</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet: </t>
+        </is>
+      </c>
+    </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sheet: </t>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>101626</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4599,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>101626</t>
+          <t>101728</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4226,7 +4616,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>101728</t>
+          <t>101763</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4243,7 +4633,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4260,29 +4650,54 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>101885</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Marcus, David</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRB</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4294,12 +4709,22 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>101626</t>
+          <t>101728</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4311,12 +4736,22 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>101728</t>
+          <t>101763</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4328,12 +4763,22 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>101788</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 170.0</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 157.3</t>
         </is>
       </c>
     </row>
@@ -4345,12 +4790,22 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>101788</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4817,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>101885</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4370,46 +4825,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>2252</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRCH (YTD)</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRCH (YTD)</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>101656</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4886,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>101656</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -4438,7 +4903,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>101683</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -4455,7 +4920,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -4472,12 +4937,27 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Ricchetti, Bryan</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRCH</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4969,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -4501,17 +4981,27 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 176.0</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 305.30000000000007</t>
         </is>
       </c>
     </row>
@@ -4523,12 +5013,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>101597</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4540,12 +5040,22 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>101656</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4557,12 +5067,22 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>101683</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -4574,12 +5094,22 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -4591,12 +5121,22 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 57.800000000000004</t>
         </is>
       </c>
     </row>
@@ -4608,7 +5148,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4616,46 +5156,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>5445</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="82"/>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Chicago</t>
+        </is>
+      </c>
+    </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Chicago</t>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>101656</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4667,7 +5217,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>101656</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -4684,7 +5234,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>101683</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4701,7 +5251,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4718,12 +5268,27 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Ricchetti, Bryan</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRCH</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
@@ -4735,7 +5300,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4747,17 +5312,27 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 176.0</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 305.30000000000007</t>
         </is>
       </c>
     </row>
@@ -4769,12 +5344,22 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>101597</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4786,12 +5371,22 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>101656</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4803,12 +5398,22 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>101683</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -4820,12 +5425,22 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -4837,12 +5452,22 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 57.800000000000004</t>
         </is>
       </c>
     </row>
@@ -4854,7 +5479,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -4862,46 +5487,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>5445</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="98"/>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRDC (YTD)</t>
+        </is>
+      </c>
+    </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRDC (YTD)</t>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>101168</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4913,7 +5548,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>101168</t>
+          <t>101525</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -4930,7 +5565,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>101525</t>
+          <t>101890</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -4947,7 +5582,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>101890</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -4964,7 +5599,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -4981,7 +5616,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>102175</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -4993,17 +5628,27 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>101168</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5015,12 +5660,22 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>101168</t>
+          <t>101525</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5687,22 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>101525</t>
+          <t>101890</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5714,22 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>101890</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -5066,12 +5741,22 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5768,22 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>102175</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 88.0</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5795,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -5108,105 +5803,125 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>6245</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="114"/>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="113"/>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRLA (YTD)</t>
+        </is>
+      </c>
+    </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRLA (YTD)</t>
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>101210</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>101210</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="118"/>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRNY (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
           <t>MISSING IN DB</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>101210</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>101210</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="119"/>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRNY (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>101046</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5933,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>101046</t>
+          <t>101559</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -5235,7 +5950,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>101559</t>
+          <t>101620</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -5247,17 +5962,27 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>101620</t>
+          <t>101046</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5269,12 +5994,22 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>101046</t>
+          <t>101559</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5286,7 +6021,7 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>101559</t>
+          <t>101620</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -5294,46 +6029,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>101620</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="128"/>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRSF (YTD)</t>
+        </is>
+      </c>
+    </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRSF (YTD)</t>
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>101226</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5345,7 +6090,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>101226</t>
+          <t>101468</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -5362,7 +6107,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>101468</t>
+          <t>101647</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -5374,17 +6119,27 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>101647</t>
+          <t>101226</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -5396,12 +6151,22 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>101226</t>
+          <t>101468</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5413,7 +6178,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>101468</t>
+          <t>101647</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -5421,46 +6186,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>101647</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="137"/>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="136"/>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRSV (YTD)</t>
+        </is>
+      </c>
+    </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRSV (YTD)</t>
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>101461</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5472,7 +6247,7 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>101677</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -5489,7 +6264,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>101682</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -5506,29 +6281,54 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Feitzinger, Kristin</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRMP</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>101400</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 162.80000000000007</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 169.50000000000003</t>
         </is>
       </c>
     </row>
@@ -5540,12 +6340,22 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5557,12 +6367,22 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>101677</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5574,12 +6394,22 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>101682</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5591,7 +6421,7 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -5599,46 +6429,56 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="149"/>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 13.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="148"/>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: SV</t>
+        </is>
+      </c>
+    </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: SV</t>
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>101461</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5650,7 +6490,7 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>101677</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -5667,7 +6507,7 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>101682</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -5684,29 +6524,54 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Feitzinger, Kristin</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRMP</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>101400</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 162.80000000000007</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 169.50000000000003</t>
         </is>
       </c>
     </row>
@@ -5718,12 +6583,22 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5735,12 +6610,22 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>101677</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5752,12 +6637,22 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>101682</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5769,7 +6664,7 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -5777,21 +6672,14 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 13.4</t>
         </is>
       </c>
     </row>

--- a/tests/TeamworkDB/output/utilization_failures_report_202604.xlsx
+++ b/tests/TeamworkDB/output/utilization_failures_report_202604.xlsx
@@ -604,8 +604,8 @@
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
@@ -680,22 +680,22 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>693.40</t>
+          <t>794.30</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>751.20</t>
+          <t>857.20</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>57.80</t>
+          <t>62.90</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>8.34%</t>
+          <t>7.92%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>236.80</t>
+          <t>363.80</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>250.20</t>
+          <t>380.50</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>16.70</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>4.59%</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>890,690.00</t>
+          <t>1,018,075.00</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>974,500.00</t>
+          <t>1,109,280.00</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>83,810.00</t>
+          <t>91,205.00</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>9.41%</t>
+          <t>8.96%</t>
         </is>
       </c>
     </row>
@@ -791,22 +791,22 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>310,827.00</t>
+          <t>470,070.00</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>329,587.00</t>
+          <t>493,450.00</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>18,760.00</t>
+          <t>23,380.00</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>4.97%</t>
         </is>
       </c>
     </row>
@@ -947,22 +947,22 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2,658.90</t>
+          <t>2,759.80</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2,918.60</t>
+          <t>3,024.60</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>259.70</t>
+          <t>264.80</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>9.77%</t>
+          <t>9.59%</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>15,066.50</t>
+          <t>15,956.80</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>15,622.60</t>
+          <t>16,512.90</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.49%</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1021,22 +1021,22 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>15,558.50</t>
+          <t>3,481.70</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>16,029.40</t>
+          <t>3,659.10</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>470.90</t>
+          <t>177.40</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>5.10%</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1058,22 +1058,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3,338.30</t>
+          <t>3,949.90</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>3,515.70</t>
+          <t>4,178.00</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>177.40</t>
+          <t>228.10</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>5.31%</t>
+          <t>5.77%</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1095,29 +1095,29 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>3,817.40</t>
+          <t>1,047.00</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>4,045.50</t>
+          <t>1,209.30</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>228.10</t>
+          <t>162.30</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>5.98%</t>
+          <t>15.50%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRCH</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1127,39 +1127,39 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>920.00</t>
+          <t>3,534,114.00</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>1,079.00</t>
+          <t>3,918,074.00</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>159.00</t>
+          <t>383,960.00</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>17.28%</t>
+          <t>10.86%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRNY</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1169,22 +1169,22 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>3,406,729.00</t>
+          <t>19,625,725.50</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>3,783,294.00</t>
+          <t>20,294,651.00</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>376,565.00</t>
+          <t>668,925.50</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>11.05%</t>
+          <t>3.41%</t>
         </is>
       </c>
     </row>
@@ -1206,22 +1206,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>7,815,936.00</t>
+          <t>8,284,580.50</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>8,138,151.00</t>
+          <t>8,606,795.00</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>322,215.00</t>
+          <t>322,214.50</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>3.89%</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8,168,391.00</t>
+          <t>8,788,926.00</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>8,439,159.00</t>
+          <t>9,059,694.00</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2,631,599.00</t>
+          <t>2,746,005.00</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2,784,163.00</t>
+          <t>2,898,569.00</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>5.56%</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3,678,480.50</t>
+          <t>3,808,907.50</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>3,889,473.00</t>
+          <t>4,019,900.00</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>5.74%</t>
+          <t>5.54%</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1,186,110.00</t>
+          <t>1,345,353.00</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>1,408,710.00</t>
+          <t>1,572,573.00</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>222,600.00</t>
+          <t>227,220.00</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>18.77%</t>
+          <t>16.89%</t>
         </is>
       </c>
     </row>
@@ -1384,11 +1384,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
@@ -1407,7 +1407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Sheet: Month - CRDC (Monthly)</t>
+          <t>Sheet: Month - CRSF (Monthly)</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>101510</t>
+          <t>101650</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Castro Cienfuegos, Nicolas</t>
+          <t>Li, Lily</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1466,178 +1466,178 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>94.00</t>
+          <t>33.20</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>99.50</t>
+          <t>38.20</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>5.85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>101510</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Castro Cienfuegos, Nicolas</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>89,300.00</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>94,525.00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>5,225.00</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>5.85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>15.06%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRUK (Monthly)</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRLA (Monthly)</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>0531</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Tilson, Hannah</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>159.60</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>168.00</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>8.40</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>101827</t>
+          <t>101659</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Aron, Kartik</t>
+          <t>Honnor, Kaman</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Target_Hours</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>214.20</t>
+          <t>114.00</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>223.20</t>
+          <t>120.00</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>101827</t>
+          <t>101963</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Aron, Kartik</t>
+          <t>Chakma, Tridevi</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Standard_Rev</t>
+          <t>Target_Hours</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>93,177.00</t>
+          <t>152.00</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>97,092.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>3,915.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
@@ -1645,521 +1645,422 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Sheet: Month - CRNY (Monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+          <t>MISSING ROWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRB  (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>101697</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Lehrer, Nimrod David</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Actual_Hours</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>79.90</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>94.00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>14.10</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>17.65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>101697</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Lehrer, Nimrod David</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>68,714.00</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>80,840.00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>12,126.00</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>17.65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>101967</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRSF (Monthly)</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2252</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Marcus, David</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRB</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>5196</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>101650</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Li, Lily</t>
+          <t>101967</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>33.20</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>38.20</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>15.06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2252</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 7.3999999999999995</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRUK (Monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>5196</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet: </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>0531</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Tilson, Hannah</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>159.60</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>168.00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>8.40</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>101659</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Honnor, Kaman</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>114.00</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>120.00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>101963</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chakma, Tridevi</t>
+          <t>101967</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>152.00</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>160.00</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2252</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Marcus, David</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRB</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 7.4000</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>MISSING ROWS</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>5196</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>101967</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRB  (Monthly)</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2252</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 7.3999999999999995</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>5196</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRCH (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>101967</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>2252</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Marcus, David</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRB</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 7.4000</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>5196</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>101967</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 4.8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2169,169 +2070,169 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>Employee_name: Ricchetti, Bryan</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRCH</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 62.9000</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>101899</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
           <t>Target_Hrs: 0.0</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sheet: </t>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>102118</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>4709</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 62.900000000000006</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Chicago</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>101967</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2252</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Marcus, David</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRB</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 7.4000</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>5196</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>101967</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 4.8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2341,157 +2242,157 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>Employee_name: Ricchetti, Bryan</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRCH</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 62.9000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>101899</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
           <t>Target_Hrs: 0.0</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRCH (Monthly)</t>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>102118</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>4709</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 62.900000000000006</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRDC (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>101899</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>102118</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Ricchetti, Bryan</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRCH</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2404,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2518,49 +2419,59 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 57.800000000000004</t>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Chicago</t>
-        </is>
-      </c>
-    </row>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>5936</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>101899</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2483,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -2589,27 +2500,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Ricchetti, Bryan</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRCH</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2517,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -2648,7 +2544,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2667,55 +2563,60 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 57.800000000000004</t>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRNY (Monthly)</t>
+        </is>
+      </c>
+    </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRDC (Monthly)</t>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>101327</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Nathans, Dora</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 2.3000</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2628,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>101334</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -2744,7 +2645,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>101692</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2756,12 +2657,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2771,12 +2672,17 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Employee_name: Zhao, Juliana</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 4.5000</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2694,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>101327</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2798,167 +2704,243 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>101334</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
           <t>Target_Hrs: 0.0</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
-    <row r="72"/>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRNY (Monthly)</t>
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>101692</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>6390</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: NY</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>101334</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>101692</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>101334</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
+          <t>101327</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Nathans, Dora</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 2.3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>101334</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
           <t>101692</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRSF (Monthly)</t>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>6390</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Zhao, Juliana</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 4.5000</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>101226</t>
+          <t>101327</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 2.3</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2952,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>101226</t>
+          <t>101334</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2989,77 +2971,82 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>101692</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRSV (Monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>6390</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRSF (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>101515</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Feitzinger, Kristin</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRMP</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3058,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>101226</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -3083,27 +3070,17 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>101515</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3092,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>101226</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -3125,12 +3102,12 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 0.0</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 13.4</t>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3119,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -3165,7 +3142,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Sheet: SV</t>
+          <t>Sheet: Month - CRSV (Monthly)</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3279,7 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 13.4</t>
+          <t>Actual_Hrs: 16.7</t>
         </is>
       </c>
     </row>
@@ -3328,6 +3305,178 @@
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: SV</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>101515</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Feitzinger, Kristin</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRMP</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 16.7000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>6063</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>101515</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 16.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>6063</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 0.0</t>
         </is>
@@ -3344,11 +3493,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
@@ -3500,12 +3649,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>581.10</t>
+          <t>592.70</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>353.00</t>
+          <t>364.60</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -3515,7 +3664,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>39.25%</t>
+          <t>38.48%</t>
         </is>
       </c>
     </row>
@@ -3537,12 +3686,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>537,517.50</t>
+          <t>548,247.50</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>326,525.00</t>
+          <t>337,255.00</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -3552,7 +3701,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>39.25%</t>
+          <t>38.48%</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3842,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>651.60</t>
+          <t>652.20</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>384.90</t>
+          <t>385.50</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -3708,7 +3857,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>40.93%</t>
+          <t>40.89%</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3879,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>316,026.00</t>
+          <t>316,317.00</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>186,677.00</t>
+          <t>186,968.00</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -3745,7 +3894,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>40.93%</t>
+          <t>40.89%</t>
         </is>
       </c>
     </row>
@@ -3871,12 +4020,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>101697</t>
+          <t>101788</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Lehrer, Nimrod David</t>
+          <t>Rocafort, Roland</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3886,22 +4035,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>459.20</t>
+          <t>571.50</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>473.30</t>
+          <t>418.40</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>153.10</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>26.79%</t>
         </is>
       </c>
     </row>
@@ -3918,240 +4067,240 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>328,612.50</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>240,580.00</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>88,032.50</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>26.79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRSF (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>101650</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Li, Lily</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
           <t>Actual_Hours</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>555.20</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>402.10</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>153.10</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>27.58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>101697</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Lehrer, Nimrod David</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>394,912.00</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>407,038.00</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>12,126.00</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>3.07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>101788</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Rocafort, Roland</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Standard_Rev</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>319,240.00</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>231,208.00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>88,032.00</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>27.58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRSF (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>165.70</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>170.70</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>3.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRUK (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Util Report</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Diff%</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>101650</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Li, Lily</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Actual_Hours</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>165.70</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>170.70</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>3.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRUK (YTD)</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>0531</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Tilson, Hannah</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>630.80</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>664.00</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>33.20</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>101659</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Honnor, Kaman</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Target_Hours</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>585.20</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>616.00</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>30.80</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>0531</t>
+          <t>101963</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Tilson, Hannah</t>
+          <t>Chakma, Tridevi</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -4161,17 +4310,17 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>630.80</t>
+          <t>547.20</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>664.00</t>
+          <t>576.00</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>28.80</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -4180,77 +4329,11 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>101659</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Honnor, Kaman</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>585.20</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>616.00</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>30.80</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>101963</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Chakma, Tridevi</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>547.20</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>576.00</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>28.80</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>MISSING ROWS</t>
         </is>
       </c>
     </row>
@@ -4258,32 +4341,58 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MISSING ROWS</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
+          <t>Sheet: YTD - CRB  (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRB  (YTD)</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>101626</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>101728</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4404,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>101626</t>
+          <t>101763</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -4312,7 +4421,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>101728</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4329,41 +4438,66 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Marcus, David</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRB</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>101885</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>101728</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -4373,17 +4507,12 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Employee_name: Marcus, David</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>OFFC: CRB</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 7.4000</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4524,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>101626</t>
+          <t>101763</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4422,7 +4551,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>101728</t>
+          <t>101788</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4432,12 +4561,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 170.0</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 173.60000000000002</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4578,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4476,7 +4605,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>101788</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -4486,91 +4615,71 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 170.0</t>
+          <t>Target_Hrs: 0.0</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 157.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>101885</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
-        </is>
-      </c>
-    </row>
+          <t>Actual_Hrs: 7.3999999999999995</t>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>2252</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 4.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet: </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sheet: </t>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>101626</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>101728</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4691,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>101626</t>
+          <t>101763</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4599,7 +4708,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>101728</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4616,41 +4725,66 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Marcus, David</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRB</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>101885</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>101728</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4660,17 +4794,12 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Employee_name: Marcus, David</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>OFFC: CRB</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 7.4000</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4811,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>101626</t>
+          <t>101763</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4709,7 +4838,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>101728</t>
+          <t>101788</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4719,12 +4848,12 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 170.0</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 173.60000000000002</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4865,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4763,7 +4892,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>101788</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4773,91 +4902,71 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 170.0</t>
+          <t>Target_Hrs: 0.0</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 157.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>101885</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
-        </is>
-      </c>
-    </row>
+          <t>Actual_Hrs: 7.3999999999999995</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>2252</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 4.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRCH (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRCH (YTD)</t>
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>101656</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>101683</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4978,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>101656</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -4886,7 +4995,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>101683</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -4903,12 +5012,27 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Ricchetti, Bryan</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRCH</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
@@ -4920,7 +5044,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -4932,12 +5056,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -4947,34 +5071,39 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Employee_name: Ricchetti, Bryan</t>
+          <t>Target_Hrs: 176.0</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>OFFC: CRCH</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 62.9000</t>
+          <t>Actual_Hrs: 305.90000000000003</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4986,7 +5115,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>101597</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -4996,12 +5125,12 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 176.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 305.30000000000007</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5142,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>101656</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -5023,12 +5152,12 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 0.0</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5169,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>101683</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -5050,12 +5179,12 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 0.0</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5196,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -5082,7 +5211,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
+          <t>Actual_Hrs: 62.900000000000006</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5223,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -5104,91 +5233,71 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 57.800000000000004</t>
-        </is>
-      </c>
-    </row>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>5445</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="81"/>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Chicago</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Chicago</t>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>101656</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>101683</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5309,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>101656</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -5217,7 +5326,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>101683</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -5234,12 +5343,27 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Ricchetti, Bryan</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRCH</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5375,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -5263,12 +5387,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -5278,34 +5402,39 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Employee_name: Ricchetti, Bryan</t>
+          <t>Target_Hrs: 176.0</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>OFFC: CRCH</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 62.9000</t>
+          <t>Actual_Hrs: 305.90000000000003</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5446,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>101597</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -5327,12 +5456,12 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 176.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 305.30000000000007</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5473,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>101656</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -5354,12 +5483,12 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 0.0</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5500,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>101683</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -5381,12 +5510,12 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 0.0</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5527,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -5413,7 +5542,7 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
+          <t>Actual_Hrs: 62.900000000000006</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5554,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -5435,91 +5564,71 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 57.800000000000004</t>
-        </is>
-      </c>
-    </row>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="95"/>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>5445</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="97"/>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRDC (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRDC (YTD)</t>
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>101168</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>101525</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5640,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>101168</t>
+          <t>101890</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -5548,7 +5657,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>101525</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -5565,7 +5674,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>101890</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -5582,7 +5691,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -5594,34 +5703,54 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>102175</t>
+          <t>101168</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>101525</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5762,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>101168</t>
+          <t>101890</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -5660,7 +5789,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>101525</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -5670,12 +5799,12 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 0.0</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5816,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>101890</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -5714,7 +5843,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -5724,12 +5853,12 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Target_Hrs: 88.0</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5870,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>102175</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -5760,151 +5889,146 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>6038</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 88.0</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
+    <row r="111"/>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRLA (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>101210</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>101210</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>6245</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="113"/>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRLA (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+    <row r="116"/>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRNY (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>101210</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>101210</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="118"/>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRNY (YTD)</t>
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>101046</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>101327</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Nathans, Dora</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 2.3000</t>
         </is>
       </c>
     </row>
@@ -5916,7 +6040,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>101046</t>
+          <t>101559</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -5933,7 +6057,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>101559</t>
+          <t>101620</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -5950,12 +6074,27 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>101620</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Zhao, Juliana</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 4.5000</t>
         </is>
       </c>
     </row>
@@ -5994,7 +6133,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>101559</t>
+          <t>101327</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -6009,7 +6148,7 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 2.3</t>
         </is>
       </c>
     </row>
@@ -6021,81 +6160,101 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
+          <t>101559</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
           <t>101620</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="E127" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
-    <row r="127"/>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>6390</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="129"/>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Sheet: YTD - CRSF (YTD)</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>101226</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>101468</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6266,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>101647</t>
+          <t>101226</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -6119,54 +6278,34 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>101226</t>
+          <t>101468</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>101468</t>
+          <t>101647</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -6178,81 +6317,101 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
+          <t>101226</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>101468</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
           <t>101647</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E135" s="5" t="inlineStr">
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
-    <row r="136"/>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138"/>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Sheet: YTD - CRSV (YTD)</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>101461</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>101677</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6423,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -6281,66 +6440,41 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>101677</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Feitzinger, Kristin</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRMP</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>101682</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 162.80000000000007</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 169.50000000000003</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -6350,12 +6484,17 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Employee_name: Feitzinger, Kristin</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>OFFC: CRMP</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6506,7 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>101400</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -6377,12 +6516,12 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 162.80000000000007</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 181.10000000000005</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6533,7 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -6421,81 +6560,101 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
+          <t>101677</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>101682</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
           <t>1127</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr">
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 13.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="148"/>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 16.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="150"/>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Sheet: SV</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="3" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B152" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C152" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>101461</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>101677</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6666,7 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -6524,66 +6683,41 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>101677</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D154" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Feitzinger, Kristin</t>
-        </is>
-      </c>
-      <c r="E154" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRMP</t>
-        </is>
-      </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>101682</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 162.80000000000007</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 169.50000000000003</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -6593,12 +6727,17 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Employee_name: Feitzinger, Kristin</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>OFFC: CRMP</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6749,7 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>101400</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -6620,12 +6759,12 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 162.80000000000007</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 181.10000000000005</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6776,7 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -6664,22 +6803,76 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
+          <t>101677</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>101682</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
           <t>1127</t>
         </is>
       </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 13.4</t>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 16.7</t>
         </is>
       </c>
     </row>

--- a/tests/TeamworkDB/output/utilization_failures_report_202604.xlsx
+++ b/tests/TeamworkDB/output/utilization_failures_report_202604.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRNY</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -717,29 +717,29 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>363.80</t>
+          <t>1,006.60</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>380.50</t>
+          <t>1,137.80</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>16.70</t>
+          <t>131.20</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>13.03%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -749,269 +749,269 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Standard_Rev</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1,018,075.00</t>
+          <t>363.80</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>1,109,280.00</t>
+          <t>380.50</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>91,205.00</t>
+          <t>16.70</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>8.96%</t>
+          <t>4.59%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>CRCH</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Officer</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>1,018,075.00</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>1,109,280.00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>91,205.00</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>8.96%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CRNY</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Officer</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>1,299,292.00</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>1,458,044.00</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>158,752.00</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>12.22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>CRSV</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Officer</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Standard_Rev</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>470,070.00</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>493,450.00</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>23,380.00</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>4.97%</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Sheet: 2026_US (YTD)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Util Report</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Diff%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>CRSV</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>3,960.32</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>4,245.20</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>284.88</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>7.19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>CRSV</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Target_Rev</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>3,829,251.83</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>4,092,784.00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>263,532.17</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>6.88%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Target_Hours</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2,759.80</t>
+          <t>3,960.32</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>3,024.60</t>
+          <t>4,245.20</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>264.80</t>
+          <t>284.88</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>9.59%</t>
+          <t>7.19%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>CRSF</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Target_Rev</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>15,956.80</t>
+          <t>3,829,251.83</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>16,512.90</t>
+          <t>4,092,784.00</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>556.10</t>
+          <t>263,532.17</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>6.88%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRCH</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1021,34 +1021,34 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>3,481.70</t>
+          <t>2,759.80</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>3,659.10</t>
+          <t>3,024.60</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>177.40</t>
+          <t>264.80</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>5.10%</t>
+          <t>9.59%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRSF</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1058,22 +1058,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3,949.90</t>
+          <t>15,956.80</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>4,178.00</t>
+          <t>16,512.90</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>228.10</t>
+          <t>556.10</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>5.77%</t>
+          <t>3.49%</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1095,108 +1095,108 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>1,047.00</t>
+          <t>3,481.70</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>1,209.30</t>
+          <t>3,659.10</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>162.30</t>
+          <t>177.40</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>15.50%</t>
+          <t>5.10%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>CRCH</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Standard_Rev</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3,534,114.00</t>
+          <t>3,949.90</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>3,918,074.00</t>
+          <t>4,178.00</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>383,960.00</t>
+          <t>228.10</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>10.86%</t>
+          <t>5.77%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>CRNY</t>
+          <t>CRSV</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Standard_Rev</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>19,625,725.50</t>
+          <t>1,047.00</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>20,294,651.00</t>
+          <t>1,209.30</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>668,925.50</t>
+          <t>162.30</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>15.50%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>CRSF</t>
+          <t>CRCH</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1206,29 +1206,29 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>8,284,580.50</t>
+          <t>3,534,114.00</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>8,606,795.00</t>
+          <t>3,918,074.00</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>322,214.50</t>
+          <t>383,960.00</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>10.86%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRNY</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -1243,34 +1243,34 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8,788,926.00</t>
+          <t>19,625,725.50</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>9,059,694.00</t>
+          <t>20,312,111.00</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>270,768.00</t>
+          <t>686,385.50</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.50%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>CRSV</t>
+          <t>CRSF</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1280,22 +1280,22 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2,746,005.00</t>
+          <t>8,284,580.50</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2,898,569.00</t>
+          <t>8,606,795.00</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>152,564.00</t>
+          <t>322,214.50</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>3.89%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3,808,907.50</t>
+          <t>8,788,926.00</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>4,019,900.00</t>
+          <t>9,059,694.00</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>210,992.50</t>
+          <t>270,768.00</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -1344,30 +1344,104 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>2,746,005.00</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>2,898,569.00</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>152,564.00</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>5.56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>CRSV</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>3,808,907.50</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>4,019,900.00</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>210,992.50</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>5.54%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>CRSV</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t>Officer</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Standard_Rev</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>1,345,353.00</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>1,572,573.00</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>227,220.00</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>16.89%</t>
         </is>
@@ -1384,16 +1458,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1407,7 +1481,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Sheet: Month - CRSF (Monthly)</t>
+          <t>Sheet: Month - CRNY (Monthly)</t>
         </is>
       </c>
     </row>
@@ -1451,405 +1525,455 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>101322</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Khanna, Aryan</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>129.00</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>165.00</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>36.00</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>27.91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>5674</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Li Bergolis, Matteo</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>139.70</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>131.20</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>1543.53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>101322</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Khanna, Aryan</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>62,565.00</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>80,025.00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>17,460.00</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>27.91%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>5674</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Li Bergolis, Matteo</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>10,285.00</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>169,037.00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>158,752.00</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>1543.53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRSF (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>101650</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Li, Lily</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Actual_Hours</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>33.20</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>38.20</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>15.06%</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sheet: Month - CRUK (Monthly)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Util Report</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Diff</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Diff%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>0531</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Tilson, Hannah</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>159.60</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>168.00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>8.40</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>101659</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Honnor, Kaman</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>114.00</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>120.00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>101963</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Chakma, Tridevi</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>152.00</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>160.00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>MISSING ROWS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRB  (Monthly)</t>
-        </is>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>5570</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ayhan, Alex</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>140.10</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>175.80</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>35.70</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>25.48%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>Ayhan, Alex</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>124,157.88</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>155,796.00</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>31,638.12</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>25.48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>MISSING ROWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRB  (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
           <t>101967</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>2252</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Employee_name: Marcus, David</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>OFFC: CRB</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>5196</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>101967</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>2252</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 7.3999999999999995</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>5196</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sheet: </t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1860,13 +1984,23 @@
       <c r="C26" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1881,24 +2015,19 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Employee_name: Marcus, David</t>
+          <t>Target_Hrs: 0.0</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>OFFC: CRB</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 7.4000</t>
+          <t>Actual_Hrs: 7.3999999999999995</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1911,289 +2040,284 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet: </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>101967</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>2252</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 7.3999999999999995</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Marcus, David</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRB</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 7.4000</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>5196</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRCH (Monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>101967</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 7.3999999999999995</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>5196</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRCH (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>101899</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>102118</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
           <t>4709</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Employee_name: Ricchetti, Bryan</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>OFFC: CRCH</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Total_Billable_Hours: 62.9000</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>101899</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>102118</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 62.900000000000006</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Chicago</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -2204,13 +2328,23 @@
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -2221,13 +2355,23 @@
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -2242,157 +2386,157 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 62.900000000000006</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Chicago</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>101899</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>102118</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>4709</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
           <t>Employee_name: Ricchetti, Bryan</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>OFFC: CRCH</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>Total_Billable_Hours: 62.9000</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>101899</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>102118</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 62.900000000000006</t>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRDC (Monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2404,74 +2548,64 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
+          <t>4709</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 62.900000000000006</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRDC (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
           <t>101993</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>5936</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: DC</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2617,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -2495,17 +2629,27 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
@@ -2517,74 +2661,64 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
+          <t>5936</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
           <t>101993</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>5936</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRNY (Monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -2596,56 +2730,51 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>101327</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Nathans, Dora</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRNY</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 2.3000</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>101334</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>101692</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2653,102 +2782,51 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>6390</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Zhao, Juliana</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRNY</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 4.5000</t>
-        </is>
-      </c>
-    </row>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>101327</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 2.3</t>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRNY (Monthly)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>101334</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>101692</t>
+          <t>101327</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2758,76 +2836,122 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Employee_name: Nathans, Dora</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 2.3000</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
+          <t>101334</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>101692</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
           <t>6390</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Zhao, Juliana</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 4.5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>101327</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 4.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: NY</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 2.3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>101327</t>
+          <t>101334</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -2837,46 +2961,51 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Employee_name: Nathans, Dora</t>
+          <t>Target_Hrs: 0.0</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>OFFC: CRNY</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 2.3000</t>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>101334</t>
+          <t>101692</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>101692</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -2884,129 +3013,68 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>6390</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Zhao, Juliana</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRNY</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 4.5000</t>
-        </is>
-      </c>
-    </row>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81"/>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>101327</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 2.3</t>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRSF (Monthly)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>101334</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>101692</t>
+          <t>101226</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -3014,112 +3082,112 @@
           <t>nan</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 4.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="86"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>101226</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRSF (Monthly)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>5566</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Month - CRSV (Monthly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>101226</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>5566</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>101226</t>
+          <t>101515</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -3129,49 +3197,100 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
+          <t>Employee_name: Feitzinger, Kristin</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRMP</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 16.7000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>6063</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>101515</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
           <t>Target_Hrs: 0.0</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Month - CRSV (Monthly)</t>
-        </is>
-      </c>
-    </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 16.7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>101515</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -3179,171 +3298,171 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Feitzinger, Kristin</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRMP</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 16.7000</t>
-        </is>
-      </c>
-    </row>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97"/>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>6063</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: SV</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>101515</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>101515</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 16.7</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Employee_name: Feitzinger, Kristin</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>OFFC: CRMP</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 16.7000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
           <t>6063</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>101515</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: 0.0</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E103" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: SV</t>
-        </is>
-      </c>
-    </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 16.7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN DB</t>
+          <t>MISSING IN XLS</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>101515</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -3351,132 +3470,12 @@
           <t>nan</t>
         </is>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Feitzinger, Kristin</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRMP</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 16.7000</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>6063</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>101515</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: 0.0</t>
         </is>
       </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 16.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>6063</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
+      <c r="E105" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 0.0</t>
         </is>
@@ -3493,11 +3492,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
@@ -4020,12 +4019,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>101788</t>
+          <t>101322</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Rocafort, Roland</t>
+          <t>Khanna, Aryan</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -4035,22 +4034,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>571.50</t>
+          <t>509.40</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>418.40</t>
+          <t>545.40</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>153.10</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>26.79%</t>
+          <t>7.07%</t>
         </is>
       </c>
     </row>
@@ -4067,109 +4066,175 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>571.50</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>418.40</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>153.10</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>26.79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>5674</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Li Bergolis, Matteo</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>439.80</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>571.00</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>131.20</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>29.83%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>101322</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Khanna, Aryan</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
           <t>Standard_Rev</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>247,059.00</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>264,519.00</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>17,460.00</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>7.07%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>101788</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Rocafort, Roland</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>328,612.50</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>240,580.00</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>88,032.50</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>26.79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: YTD - CRSF (YTD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>EmpNo</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Util Report</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Diff%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>101650</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Li, Lily</t>
+          <t>Li Bergolis, Matteo</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Actual_Hours</t>
+          <t>Standard_Rev</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>165.70</t>
+          <t>532,158.00</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>170.70</t>
+          <t>690,910.00</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>158,752.00</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>29.83%</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4242,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Sheet: YTD - CRUK (YTD)</t>
+          <t>Sheet: YTD - CRSF (YTD)</t>
         </is>
       </c>
     </row>
@@ -4221,195 +4286,189 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>0531</t>
+          <t>101650</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Tilson, Hannah</t>
+          <t>Li, Lily</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Target_Hours</t>
+          <t>Actual_Hours</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>630.80</t>
+          <t>165.70</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>664.00</t>
+          <t>170.70</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>33.20</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>101659</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Honnor, Kaman</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>585.20</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>616.00</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>30.80</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-    </row>
+          <t>3.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>101963</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Chakma, Tridevi</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Target_Hours</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>547.20</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>576.00</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>28.80</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>5.26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: YTD - CRUK (YTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>EmpNo</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Util Report</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Diff%</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>5570</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Ayhan, Alex</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Actual_Hours</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>496.60</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>532.30</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>35.70</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>7.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>5570</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Ayhan, Alex</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Standard_Rev</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>446,819.17</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>478,457.00</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>31,637.83</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>7.08%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>MISSING ROWS</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Sheet: YTD - CRB  (YTD)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>101626</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>101728</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>101763</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4480,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>101885</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -4438,93 +4497,58 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>101728</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Marcus, David</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRB</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>101626</t>
+          <t>101763</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>101728</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4534,12 +4558,17 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Employee_name: Marcus, David</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>OFFC: CRB</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4580,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>101788</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -4561,12 +4590,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 170.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 173.60000000000002</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4607,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>101885</t>
+          <t>101728</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4605,98 +4634,128 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
+          <t>101763</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>101788</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 170.0</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 173.60000000000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>101885</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>2252</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: 0.0</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 7.3999999999999995</t>
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Sheet: </t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>101626</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>101728</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>101763</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4767,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>101885</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4725,93 +4784,58 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>101728</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Marcus, David</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRB</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>101626</t>
+          <t>101763</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>101728</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4821,12 +4845,17 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Employee_name: Marcus, David</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>OFFC: CRB</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 7.4000</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4867,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>101788</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4848,12 +4877,12 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 170.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 173.60000000000002</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4894,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>101885</t>
+          <t>101728</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4892,98 +4921,128 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
+          <t>101763</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>101788</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 170.0</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 173.60000000000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>101885</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
           <t>2252</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: 0.0</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 7.3999999999999995</t>
         </is>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Sheet: YTD - CRCH (YTD)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>101656</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>101683</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>101899</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4995,7 +5054,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -5012,27 +5071,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Ricchetti, Bryan</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRCH</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5088,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -5056,39 +5100,29 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>101597</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 176.0</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 305.90000000000003</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>101656</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -5098,39 +5132,34 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Employee_name: Ricchetti, Bryan</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>OFFC: CRCH</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>101683</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5171,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -5152,12 +5181,12 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Target_Hrs: 176.0</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
+          <t>Actual_Hrs: 305.90000000000003</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5198,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -5179,12 +5208,12 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5225,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -5206,12 +5235,12 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 62.900000000000006</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5223,98 +5252,128 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
+          <t>101899</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>102118</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>4709</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 62.900000000000006</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
           <t>5445</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Sheet: Chicago</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>101656</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>101683</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>101899</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5385,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -5343,27 +5402,12 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Ricchetti, Bryan</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRCH</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5419,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -5387,39 +5431,29 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>101597</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 176.0</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 305.90000000000003</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>101656</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -5429,39 +5463,34 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Employee_name: Ricchetti, Bryan</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>OFFC: CRCH</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 62.9000</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>101683</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5502,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -5483,12 +5512,12 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Target_Hrs: 176.0</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
+          <t>Actual_Hrs: 305.90000000000003</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5529,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -5510,12 +5539,12 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5556,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>101683</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -5537,12 +5566,12 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 62.900000000000006</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5554,98 +5583,128 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
+          <t>101899</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>102118</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>4709</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 62.900000000000006</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
           <t>5445</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Sheet: YTD - CRDC (YTD)</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>101168</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>101525</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>101890</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5716,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>101168</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -5674,7 +5733,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>102175</t>
+          <t>101525</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -5691,7 +5750,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>101890</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -5703,81 +5762,51 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>101168</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>101525</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>101890</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5818,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>101168</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -5799,12 +5828,12 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 0.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: 0.0</t>
+          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5845,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>102175</t>
+          <t>101525</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -5843,7 +5872,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>101890</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -5853,7 +5882,7 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: 88.0</t>
+          <t>Target_Hrs: None</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -5870,182 +5899,197 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
+          <t>101993</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>102175</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>6038</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 88.0</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
           <t>6245</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E110" s="5" t="inlineStr">
+      <c r="E113" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
-    <row r="111"/>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Sheet: YTD - CRLA (YTD)</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN DB</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>101210</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN XLS</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>101210</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E115" s="5" t="inlineStr">
+      <c r="E118" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
-    <row r="116"/>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="119"/>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Sheet: YTD - CRNY (YTD)</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>101046</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>101327</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Nathans, Dora</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRNY</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 2.3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>101559</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -6057,7 +6101,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>101620</t>
+          <t>101046</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -6074,7 +6118,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>101327</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -6084,7 +6128,7 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Employee_name: Zhao, Juliana</t>
+          <t>Employee_name: Nathans, Dora</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -6094,73 +6138,53 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>Total_Billable_Hours: 4.5000</t>
+          <t>Total_Billable_Hours: 2.3000</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>101046</t>
+          <t>101559</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>101327</t>
+          <t>101620</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 2.3</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>101559</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -6170,12 +6194,17 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Employee_name: Zhao, Juliana</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>OFFC: CRNY</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 4.5000</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6216,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>101620</t>
+          <t>101046</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -6214,105 +6243,135 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
+          <t>101327</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>101559</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>101620</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
           <t>6390</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E131" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 4.5</t>
         </is>
       </c>
     </row>
-    <row r="129"/>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="132"/>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>Sheet: YTD - CRSF (YTD)</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>101226</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>101468</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="inlineStr">
-        <is>
-          <t>101647</t>
-        </is>
-      </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -6323,23 +6382,13 @@
       <c r="C135" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 0.0</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 0.0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -6350,23 +6399,13 @@
       <c r="C136" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -6379,90 +6418,110 @@
           <t>nan</t>
         </is>
       </c>
-      <c r="D137" s="5" t="inlineStr">
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>101226</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: 0.0</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: 0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>101468</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E137" s="5" t="inlineStr">
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
-    <row r="138"/>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>101647</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="141"/>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Sheet: YTD - CRSV (YTD)</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr">
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>101461</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>101677</t>
-        </is>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>101682</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -6474,93 +6533,58 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D144" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Feitzinger, Kristin</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRMP</t>
-        </is>
-      </c>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>101677</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 162.80000000000007</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 181.10000000000005</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>101682</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D146" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -6570,12 +6594,17 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Employee_name: Feitzinger, Kristin</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>OFFC: CRMP</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6616,7 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>101400</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -6597,12 +6626,12 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 162.80000000000007</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 181.10000000000005</t>
         </is>
       </c>
     </row>
@@ -6614,98 +6643,128 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
+          <t>101461</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>101677</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>101682</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
           <t>1127</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E149" s="5" t="inlineStr">
+      <c r="E152" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 16.7</t>
         </is>
       </c>
     </row>
-    <row r="150"/>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="153"/>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Sheet: SV</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B155" s="3" t="inlineStr">
         <is>
           <t>EmpNo</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t>Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>101461</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>101677</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>MISSING IN DB</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>101682</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
         </is>
       </c>
     </row>
@@ -6717,93 +6776,58 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="inlineStr">
-        <is>
-          <t>Employee_name: Feitzinger, Kristin</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>OFFC: CRMP</t>
-        </is>
-      </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>101677</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: 162.80000000000007</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: 181.10000000000005</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>101461</t>
+          <t>101682</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="D158" s="5" t="inlineStr">
-        <is>
-          <t>Target_Hrs: None</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>Actual_Hrs: None</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>MISSING IN XLS</t>
+          <t>MISSING IN DB</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -6813,12 +6837,17 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Employee_name: Feitzinger, Kristin</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>OFFC: CRMP</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Total_Billable_Hours: 16.7000</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6859,7 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>101400</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -6840,12 +6869,12 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Target_Hrs: None</t>
+          <t>Target_Hrs: 162.80000000000007</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Actual_Hrs: None</t>
+          <t>Actual_Hrs: 181.10000000000005</t>
         </is>
       </c>
     </row>
@@ -6857,20 +6886,101 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
+          <t>101461</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>101677</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>101682</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>Target_Hrs: None</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>Actual_Hrs: None</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>MISSING IN XLS</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
           <t>1127</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
         <is>
           <t>Target_Hrs: None</t>
         </is>
       </c>
-      <c r="E161" s="5" t="inlineStr">
+      <c r="E164" s="5" t="inlineStr">
         <is>
           <t>Actual_Hrs: 16.7</t>
         </is>
